--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0078.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0078.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Chúng ta cũng gặp vài trở ngại ở Khu Phố Cổ Septimont. Những tín đồ ở đó đang yêu cầu hỗ trợ từ Cộng Hưởng Giả và Echo Thường.</t>
+          <t>Chúng ta cũng gặp vài trở ngại ở Khu Phố Cổ Septimont. Những tín đồ ở đó đang yêu cầu hỗ trợ từ Resonator và Echo Thường.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Okay..</t>
+          <t>Ừm...</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Ta cũng vậy.</t>
+          <t>Tao cũng vậy.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Haha, đúng lúc quá, cậu {Male=bé trai;Female=bé gái} ơi! Ta đang chuẩn bị một vở kịch mới, và đang rất cần một anh hùng nhanh nhẹn đấy!</t>
+          <t>Haha, đúng lúc quá, cậu {Male=boy;Female=girl} ơi! Ta đang chuẩn bị một vở kịch mới, và đang rất cần một anh hùng nhanh nhẹn đấy!</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Andreas! Chúng ta đã là đồng đội bao lâu rồi? Sao chẳng có tý ăn ý nào thế? Câu nói đùa của ta còn chưa trúng đích kìa!</t>
+          <t>Andreas! Chúng ta đã là đồng đội bao lâu rồi? Sao chẳng có tý ăn ý nào thế? Câu nói đùa của tao còn chưa trúng đích kìa!</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Không, không, cậu {Male=con trai;Female=con gái} ấy cười nhạo lời tớ đấy. Giờ chính tớ lại thành trò cười thứ hai mươi mốt rồi, chỉ còn hai mươi trò nữa thôi!</t>
+          <t>Không, không, cậu {Male=boy;Female=girl} ấy cười nhạo lời tớ đấy. Giờ chính tớ lại thành trò cười thứ hai mươi mốt rồi, chỉ còn hai mươi trò nữa thôi!</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Nghĩ lại thì, nếu Brant đưa cậu lên đúng con tàu, cậu đã chẳng phải lạc vào Mournfell Canyon… Nói cho cùng, lỗi là do Brant.</t>
+          <t>Nghĩ lại thì, nếu Brant đưa mày lên đúng con tàu, mày đã chẳng phải lạc vào Mournfell Canyon… Nói cho cùng, lỗi là do Brant.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Càng lý do để gọi đó là vấn đề của Brant. Hắn bảo tiếng cười phải lan tỏa khắp mọi ngóc ngách thế giới. Rõ ràng là nó đã bỏ sót chỗ của ngươi rồi!</t>
+          <t>Càng lý do để gọi đó là vấn đề của Brant. Hắn bảo tiếng cười phải lan tỏa khắp mọi ngóc ngách thế giới. Rõ ràng là nó đã bỏ sót chỗ của mày rồi!</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Thử thách? Ngươi bảo ta phải chịu thử thách à?! Hahaha. Chẳng ai có quyền thử thách &lt;i&gt;ta&lt;/i&gt; đâu.</t>
+          <t>Thử thách? Mày bảo tao phải chịu thử thách à?! Hahaha. Chẳng ai có quyền thử thách &lt;i&gt;tao&lt;/i&gt; đâu.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>...Ngươi khiến ta phát ngán, Alessio. Từ bao giờ ngươi lại tin rằng Ragunna là thứ để chúng ta sở hữu?</t>
+          <t>...Mày khiến tao phát ngán, Alessio. Từ bao giờ mày lại tin rằng Ragunna là thứ để chúng ta sở hữu?</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Nó khiến ta tự hỏi tại sao ngươi lại đưa ra những phán xét riêng rẽ như vậy.</t>
+          <t>Nó khiến tao tự hỏi tại sao mày lại đưa ra những phán xét riêng rẽ như vậy.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Nó khiến ta tự hỏi tại sao ngươi lại đưa ra những phán xét riêng rẽ như vậy.</t>
+          <t>Nó khiến tao tự hỏi tại sao mày lại đưa ra những phán xét riêng rẽ như vậy.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Haha, Phoebe mà ta biết đâu có để tâm mấy thứ vớ vẩn này!</t>
+          <t>Haha, Phoebe mà tao biết đâu có để tâm mấy thứ vớ vẩn này!</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Ta đã thấy gánh nặng mà cô ấy phải gánh vác trước khi đến Septimont.</t>
+          <t>Tao đã thấy gánh nặng mà cô ấy phải gánh vác trước khi đến Septimont.</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Ta sẽ đi xem sao.</t>
+          <t>Tao sẽ đi xem sao.</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Dạo này ta đi xa lắm, thấy những thứ không thể ngờ tới.</t>
+          <t>Dạo này tao đi xa lắm, thấy những thứ không thể ngờ tới.</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Hehe, thật ra, tối qua tớ có viết thư cho cô ấy. Chắc cô ấy sẽ sốc lắm khi biết không những tớ còn sống mà còn trở thành Cộng Hưởng Giả nữa.</t>
+          <t>Hehe, thật ra, tối qua tớ có viết thư cho cô ấy. Chắc cô ấy sẽ sốc lắm khi biết không những tớ còn sống mà còn trở thành Resonator nữa.</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Cậu đã trở thành Cộng Hưởng Giả rồi à?</t>
+          <t>Cậu đã trở thành Resonator rồi à?</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Này, Acolyte kia. Cậu đang lẩm bẩm với ai thế?</t>
+          <t>Này, Acolyte kia. Mày đang lẩm bẩm với ai thế?</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Tại sao?</t>
+          <t>Sao vậy?</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Ngươi có biết chính Medulius đã cứu ngươi khỏi Dark Tide không? Hắn làm vậy để cảm ơn lời cầu nguyện của ngươi đấy.</t>
+          <t>Mày có biết chính Medulius đã cứu mày khỏi Dark Tide không? Hắn làm vậy để cảm ơn lời cầu nguyện của mày đấy.</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Cậu dám quay lại Septimont hả, Julia? Cậu không được chào đón ở đây!</t>
+          <t>Mày dám quay lại Septimont hả, Julia? Mày không được chào đón ở đây!</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Sao ngươi... Này, ông kia! Đấu sĩ! Ông đứng đó làm gì? Đuổi cô ta đi ngay lập tức!</t>
+          <t>Sao mày... Này, ông kia! Đấu sĩ! Ông đứng đó làm gì? Đuổi cô ta đi ngay lập tức!</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Adric hả? Haha, đội mũ bảo hiểm làm gì. Định tránh mặt ta trước đám đông à?</t>
+          <t>Adric hả? Haha, đội mũ bảo hiểm làm gì. Định tránh mặt tao trước đám đông à?</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Ta nghe nói ngươi mạo hiểm quay về vì điền trang bên ngoài Septimont bị Hắc Triều tàn phá. Đừng lo, ta sẽ đi cùng ngươi đến nơi khác.</t>
+          <t>Tao nghe nói mày mạo hiểm quay về vì điền trang bên ngoài Septimont bị Hắc Triều tàn phá. Đừng lo, tao sẽ đi cùng mày đến nơi khác.</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Calliope và bất kỳ ai muốn đuổi ta đi, hãy tự mình kéo ta ra khỏi Hẻm Núi Mournfell!</t>
+          <t>Calliope và bất kỳ ai muốn đuổi tao đi, hãy tự mình kéo tao ra khỏi Hẻm Núi Mournfell!</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Ta nghĩ cô ấy xứng đáng nhận điều đó.</t>
+          <t>Tao nghĩ cô ấy xứng đáng nhận điều đó.</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Ta nghĩ cô ấy không đáng phải chết vì tội lỗi của mình.</t>
+          <t>Tao nghĩ cô ấy không đáng phải chết vì tội lỗi của mình.</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Thằng nhóc của cậu đâu?</t>
+          <t>Thằng nhóc của mày đâu?</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Để ta góp sức một tay.</t>
+          <t>Để tao góp sức một tay.</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Với ta thì ngon đấy!</t>
+          <t>Với tao thì ngon đấy!</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Có việc gì mà cậu lại đến Septimont vậy?</t>
+          <t>Có việc gì mà bạn lại đến Septimont vậy?</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Còn khi có việc phải làm, ta lao vào làm ngay!</t>
+          <t>Còn khi có việc phải làm, tao lao vào làm ngay!</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Tớ là Xiaobei, đến từ Kim Châu. Chúng ta đã gặp nhau ở Mỏ Hổ Nham rồi đấy!</t>
+          <t>Tớ là Xiaobei, đến từ Jinzhou. Chúng ta đã gặp nhau ở Mỏ Hổ Nham rồi đấy!</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Cậu tìm cái gì?</t>
+          <t>Mày tìm cái gì?</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Cần ta giúp không?</t>
+          <t>Cần tao giúp không?</t>
         </is>
       </c>
     </row>
